--- a/export/output.xlsx
+++ b/export/output.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="lettera_dimissione" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="eco_postoperatorio" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="intervento" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="coronarografia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lettera_dimissione" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eco_postoperatorio" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="intervento" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coronarografia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cartellino_anestesiologico" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW2"/>
+  <dimension ref="A1:EV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,6 +806,391 @@
       <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>h_stay_giorni</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>eta_al_momento_dell_intervento</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>necessita_di_trasfusioni</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>edemi_declivi</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>ascite</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>intervento_cardiochirurgico_pregresso</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>intervento_transcatetere_pregresso</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>intervento_pregresso_descrizione</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>altri_diuretici</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>statine</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>insulina</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>metformina</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>anti_sglt2</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>arni</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>pre_esami_laboratorio</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>post_esami_laboratorio</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>pre_emocromo_globuli_rossi</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>post_emocromo_globuli_rossi</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_emocromo_globuli_bianchi</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>post_emocromo_globuli_bianchi</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>pre_emocromo_ematocrito</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>post_emocromo_ematocrito</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>pre_emocromo_emoglobina</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>post_emocromo_emoglobina</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>pre_piastrine_piastrine</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>post_piastrine_piastrine</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_glucosio</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_glucosio</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_urea</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_urea</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_creatinina</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_creatinina</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>pre_egfr_ml_min</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>post_egfr_ml_min</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_sodio</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_sodio</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_potassio</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_potassio</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_calcio</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_calcio</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_bilirubina_totale</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_bilirubina_totale</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_bilirubina_diretta</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_bilirubina_diretta</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_bilirubina_indiretta</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_bilirubina_indiretta</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_aspartato_aminotransferasi</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_aspartato_aminotransferasi</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_gammaglutamiltransferasi</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_gammaglutamiltransferasi</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_fosfatasi_alcalina</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_fosfatasi_alcalina</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_latticodeidrogenasi</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_latticodeidrogenasi</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_ferro</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_ferro</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_transferrina</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_transferrina</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_albumina</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_albumina</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_proteina_c_reattiva</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_proteina_c_reattiva</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_trigliceridi</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_trigliceridi</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_colesterolo</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_colesterolo</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_troponina_t</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_troponina_t</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_creatinfosfochinasi</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_creatinfosfochinasi</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_pt_inr_international_normalized_ratio</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>post_pt_inr_international_normalized_ratio</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>pre_pt_rapporto</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>post_pt_rapporto</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>pre_aptt_secondi</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>post_aptt_secondi</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>pre_s_propeptide_natriuretico_nt_probnp</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>post_s_propeptide_natriuretico_nt_probnp</t>
         </is>
       </c>
     </row>
@@ -1079,6 +1465,489 @@
       <c r="BW2" t="n">
         <v>6</v>
       </c>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
+      <c r="DN2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="inlineStr"/>
+      <c r="DQ2" t="inlineStr"/>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr"/>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
+      <c r="EK2" t="inlineStr"/>
+      <c r="EL2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr"/>
+      <c r="EO2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr"/>
+      <c r="ER2" t="inlineStr"/>
+      <c r="ES2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr"/>
+      <c r="EV2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2019014416</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0204-04-19</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0804-04-19</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ANGELO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PELLECCHIA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3393439365</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25/02/1958</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>In data 5\4\19 intervento di plastica valvolare mitralica percutanea mediante posizionamento di dispositivo Mitraclip (singola clip).</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Insufficienza mitralica post-plastica mitralica (REDO).</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Ilb</t>
+        </is>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>plastica mitralica: resezione quadranoglare + anello Seguin 34</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>anticoagulante orale</t>
+        </is>
+      </c>
+      <c r="AP3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>37</v>
+      </c>
+      <c r="AR3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Il decorso perioperatorio è stato regolare. Il decorso in reparto è stato regolare. L'ECG alla dimissione dimostra ritmo sinusale. L'Rx torace pre-dimissione non evidenzia patologia pleuro-parenchimale in atto. L'ecocardiogramma trans-toracico pre-dimissione evidenzia esiti di Mitraclip con insufficienza residua di grado lieve moderato non stenosi residua grad medio 4mmHg assenza di versamento pericardico. L'accesso inguinale destro è in ordine. Si consiglia rimozione di punto inguinale presso il proprio medico curante tra 4-5 giorni. Gli esami di laboratorio di routine (emocromo, funzionalità renale ed epatica, elettroliti) alla dimissione sono risultati consoni con lo stato post-operatorio. Oltre a quanto sopra riportato, non sono stati eseguiti altri trattamenti farmacologici o di altro genere.</t>
+        </is>
+      </c>
+      <c r="BB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>Paziente nega allergie. Familiarità negativa per cardiopatia ischemica. Ipertensione arteriosa in terapia. Ex fumatore. Pregresso intervento di asportazione polipo corda vocale destra. Pregressa ulcera duodenale, pregressa calcolosi renale. 28 gennaio 2012 verosimile TIA nel territorio vertebro-basilare; eseguita TAC encefalo risultata nella norma. La RM Encefalo ha evidenziato piccoli plurimi focolai iperintensi in T2 e FLAIRa livello della sostanza bianca dei centri semiovali e delle corone radiate di significato vascolare microangiopatico. Non sono stati rilevati lesioni focali del troncoencefalico, da allora in terapia anticoagulante orale. Nel 2002 intervento c/o OSR di plastica mitralica: resezione quadranoglare + anello Seguin 34. Decorso postoperatorio complicato da infezione di ferita sternale. Nel 2012 durante accertamenti in seguito a TIA riscontro di insufficienza mitralica residua di grado moderato. Da allora in regolare follow-up cardiologico ed ecocardiografico con Dott Lacanna. Ultimo ecocardiogramma TT/TE (01/3/19) OSR: IM severa VC 9mm, ad origine centro-laterale, da prolasso di P2M1. VSx nella norma, DTD 57mm, FE 60%. IT lieve, PAPs 25mmHg. NYHA Ilb, RS, non edemi declivi, nega angor, nega sincopi</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>Nel 2002 intervento c/o OSR di plastica mitralica: resezione quadranoglare + anello Seguin 34</t>
+        </is>
+      </c>
+      <c r="CE3" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>Esami di laboratorio (si segnalano gli esiti significativi) Esame/Prestazione Valore Unità di misura |Intervallo Data Gruppo sanguigno A 02/04/2019 Fattore RH Positivo 02/04/2019 Ricerca Anticorpi Irregolari Negativo 02/04/2019 EMOCROMO- Globuli bianchi 10.0 1049/L 4.8 - 10.8 02/04/2019 EMOCROMO- Globuli rossi 5.08 10412/L 4.7 -6.1 02/04/2019 EMOCROMO - Emoglobina 14.8 g/dL 14 - 18 02/04/2019 EMOCROMO - Ematocrito 43.9 % 42 - 52 02/04/2019 EMOCROMO - MCV (Volume Globulare Medio) 86.4 fL 80 - 94 02/04/2019 EMOCROMO - MCHC (Conc.Emoglobinica 33.7 g Hb /dL 31 - 36 Corpusc.Media) EMOCROMO- RDW (Ind.Distribuzione Eritrocitaria) 12.6 CV % 11.5 - 14.5 02/04/2019 FORMULA - Linfociti 19.0 % 20 - 50 02/04/2019 FORMULA - Monociti 9.6 % 2-15 02/04/2019 FORMULA - Eosinofili 24 % 1-6 02/04/2019 FORMULA - Basofili 0.9 % 0-2 02/04/2019 FORMULA - Neutrofili 6.8 1049/L 1.8-7.7 02/04/2019 FORMULA - Linfociti 1.9 1049/L 1-4.8 02/04/2019 FORMULA - Monociti 1 1049/L 0.2 - 0.8 02/04/2019 FORMULA - Eosinofili 0.2 1049/L 0 - 0.45 02/04/2019 FORMULA - Basofili 0.1 1049/L 0-0.2 02/04/2019 S-GLUCOSIO 113 mg/dL 60 - 100 02/04/2019 S-BILIRUBINA INDIRETTA 0.39 mg/dL 0.01 - 0.8 02/04/2019 S-ACIDO URICO 7.7 mg/dL 2.5-7 02/04/2019 S-BILIRUBINA TOTALE 0.60 mg/dL 0.1 - 1 02/04/2019 S-BILIRUBINA DIRETTA 0.21 mg/dL 0.01 - 0.25 02/04/2019 S-SODIO 141.1 mmol/L 135 - 148 02/04/2019 S-CALCIO 2.30 mmol/L 2.1-2.6 02/04/2019 S-MAGNESIO 0.80 mmol/L 0.7 - 1 02/04/2019 S-FERRO 74 ug/dL 65 - 170 02/04/2019 S-COLINESTERASI 8.13 kU/L 5.4 - 13.2 02/04/2019 S-CREATINFOSFOCHINASI 172 U/L 20 - 195 02/04/2019 S-PROPEPTIDE NATRIURETICO NT-proBNP 55 pg/mL 0 - 227 02/04/2019 S-ASPARTATO AMINOTRANSFERASI 26 U/L 5 - 35 02/04/2019 S-ALDOLASI 11.4 U/L &lt; 7.5 02/04/2019 S-PROCALCITONINA 0.71 ng/mL &lt;0.5 02/04/2019 S-COLESTEROLO 170 mg/dL &lt; 190 02/04/2019 S-TRIGLICERIDI 178 mg/dL &lt; 150 02/04/2019 Sg-EMOGLOBINA GLICATA (HbA1c) 38 mmol/mol 20 - 42 02/04/2019 S-FOSFATASI ALCALINA 48 U/L 43 - 119 02/04/2019 S-CREATININA 1.04 mg/dL 0.5 - 1.25 02/04/2019 URINE - U-Colore Giallo 02/04/2019 Paglierino URINE - U-Aspetto Limpido 02/04/2019 URINE - U-pH 5.0 U 5-6.5 02/04/2019 URINE - U-Peso specifico 1.018 1.005 - 1.03 02/04/2019 URINE - U-Chetoni 0 mg/dL 0-0 02/04/2019 URINE - U-Emoglobina 0.00 mg/dL 0-0 02/04/2019 URINE - U-Leucociti Assenti 02/04/2019 URINE - U-Nitriti Negativo 02/04/2019 URINE - U-Bilirubina Negativa 02/04/2019 URINE - U-Urobilinogeno 0.2 EU/dL 02/04/2019 PT - INR -International Normalized Ratio- 1.46 02/04/2019 APTT - Rapporto 1.02 0.75 - 1.29 02/04/2019 S-ANTIGENE AUSTRALIA Negativo Negativo 02/04/2019 S-HBe Ag (antigene e HBV) Negativo Negativo 02/04/2019 S-ANTICORPI ANTI HBs Ag (titolo) &lt;2 mU/mL 02/04/2019 S-anti HBc Ag anticorpi IgM Negativo Negativo 02/04/2019 S-Anti HBe Ag anticorpi Negativo Negativo 02/04/2019 S-Anti HAV anticorpi IgM Negativo Negativo 02/04/2019 S-Anti HCV anticorpi totali Negativo Negativo 02/04/2019 S-ANTICORPI ed ANTIGENE p24 HIV 1-2 Negativo. La Negativo 02/04/2019 ricerca di anticorpi anti HIV puo' risultare negativa se tra infezione ed esame è trascorso un periodo inferiore a 40 giorni. Per informazioni contattare il numero 02-2643 7982/5288. S-Anti Treponema pallidum anticorpi totali Negativo Negativo 02/04/2019 S-PROTEINE TOTALI 73.3 g/L 60 - 80 02/04/2019 Albumina 60.4 % 55.8 - 66.1 02/04/2019 Alfa 1 globuline 3.8 % 2.9-4.9 02/04/2019 Beta 1 globuline 5.4 % 4.7-7.2 02/04/2019 Beta 2 globuline 6.3 % 3.2 - 6.5 02/04/2019 Gamma globuline 18.5 % 11.1 - 18.8 02/04/2019 Albumina 44.27 g/L 02/04/2019 Alfa 1 globuline 2.79 g/L 02/04/2019 Alfa 2 globuline 4.1 g/L 02/04/2019 Beta 1 globuline 3.96 g/L 02/04/2019 Beta 2 globuline 4.62 g/L 02/04/2019 Gamma globuline 13.56 g/L 02/04/2019 Beta 1 globuline 3.96 g/L 02/04/2019 Valutazione morfologica del tracciato Non alterazioni 02/04/2019 monoclonali Rapporto Albumina/Globuline 1.53 02/04/2019</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>EMOCROMO- Globuli bianchi 8.5 1049/L 4.8 - 10.8 08/04/2019 EMOCROMO - Emoglobina 14.0 g/dL 14 - 18 08/04/2019 PIASTRINE - Piastrine 161 1049/L 130 - 400 08/04/2019 S-SODIO 135.8 mmol/L 135 - 148 08/04/2019 S-POTASSIO 3.59 mmol/L 3.5 - 5 08/04/2019 S-BILIRUBINA INDIRETTA 0.22 mg/dL 0.01 - 0.8 08/04/2019 S-BILIRUBINA DIRETTA 0.22 mg/dL 0.01 - 0.25 08/04/2019 S-PROTEINA C REATTIVA 28.4 mg/L &lt;6 08/04/2019 PT - INR -International Normalized Ratio- 1.05 08/04/2019 APTT - Rapporto 0.98 0.75 - 1.29 08/04/2019</t>
+        </is>
+      </c>
+      <c r="CM3" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="n">
+        <v>10</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>14</v>
+      </c>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="n">
+        <v>161</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>113</v>
+      </c>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="n">
+        <v>141.1</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>26</v>
+      </c>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="n">
+        <v>48</v>
+      </c>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="n">
+        <v>74</v>
+      </c>
+      <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
+      <c r="EB3" t="inlineStr"/>
+      <c r="EC3" t="n">
+        <v>44.27</v>
+      </c>
+      <c r="ED3" t="inlineStr"/>
+      <c r="EE3" t="inlineStr"/>
+      <c r="EF3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="EG3" t="n">
+        <v>178</v>
+      </c>
+      <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="n">
+        <v>170</v>
+      </c>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr"/>
+      <c r="EL3" t="inlineStr"/>
+      <c r="EM3" t="n">
+        <v>172</v>
+      </c>
+      <c r="EN3" t="inlineStr"/>
+      <c r="EO3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="EP3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="EQ3" t="inlineStr"/>
+      <c r="ER3" t="inlineStr"/>
+      <c r="ES3" t="inlineStr"/>
+      <c r="ET3" t="inlineStr"/>
+      <c r="EU3" t="n">
+        <v>55</v>
+      </c>
+      <c r="EV3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1172,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1261,6 +2130,136 @@
           <t>intervento_text</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>redo</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cec</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>cannulazionearteriosa</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>statopaz</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>cardioplegia</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>approcciochirurgico</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>iniziocec</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>inizioclamp</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>inizioacc</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>fineacc</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>fineclamp</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>finecec</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>numero_1</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>eziologia_valvolare_1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>edemi_declivi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ascite</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>intervento_cardiochirurgico_pregresso</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>intervento_transcatetere_pregresso</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>intervento_pregresso_descrizione</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>anno_redo</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>altri_diuretici</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>statine</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>insulina</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>metformina</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>anti_sglt2</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>arni</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1343,6 +2342,161 @@
         <is>
           <t>Ministernotomia mediana al IV spazio intercostale. Incisione longitudinale del pericardio. L'aorta appare aneurismatica in corrispondenza della radice aortica e del tratto tubulare fino all'origine del tronco anonimo. Cannulazione del tronco brachiocefalico e dell'atrio destro per la conduzione della circolazione extracorporea. Posizionamento di un vent nella vena polmonare superiore destra. In bypass cardiopolmonare totale ipotermico si clampa l'aorta e dopo aortotomia trasversale, si infonde soluzione cardioplegica ematica fredda (Del Nido) per via anterograda selettivamente negli osti coronarici. Rimozione dell'aorta ascendente e della radice aortica. La valvola aortica appare bicuspide ed insufficiente per retrazione dei lembi e mancata coaptazione centrale. Si procede dunque alla rimozione della valvola aortica nativa ed alla preparazione dei bottoni aortici contenenti gli osti delle coronarie. Impianto di bioprotesi valvolare aortica (Inspiris Resilia n.29) su protesi tubulare vascolare (Gelweave Vascutek 32 mm) mediante sutura in polipropilene 2-0. Anastomosi prossimale del condotto valvolato a livello del piano valvolare mediante sutura continua di prolene 2-0. Confezionamento del bottone dell'ostio coronarico sinistro sul tubo valvolato mediante una sutura continua di polipropilene 5-0. Si esegue l'anastomosi distale tra tubo valvolato e moncone aortico usando una sutura continua di polipropilene 4-0. In ultimo si confeziona il bottone coronarico destro sul tubo valvolato usando una sutura continua di polipropilene 5-0. Posizionamento di vent aortico e declampaggio aortico dopo deareazione delle cavita' cardiache. Il cuore riprende a battere in ritmo sinusale. Posizionamento degli elettrodi epicardici temporanei ventricolari. Progressivo svezzamento dalla CEC in normotermia con necessità di supporto inotropo con adrenalina a medio dosaggio e supporto meccanico mediante contropulsatore aortico. Decannulazione e somministrazione di solfato di protamina. Accurata e prolungata revisione dell'emostasi. Posizionamento di due tubi di drenaggio (retrocardiaco e retrosternale). Chiusura a strati della parete toracica secondo routine.</t>
         </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>12019013470</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>COLOMBA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DE SIO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1004-04-19</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2903-03-19</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Transcatetere</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>DENTI</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PAOLO</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>VALVULOPLASTICA A CUORE APERTO DELLA VALVOLA MITRALE SENZA SOSTITUZIONE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Anestesia generale. Accesso venoso destro. Puntura transettale ecoguidata. Eparinizzazione sistemica. Inserimento del catetere guida su guida Amplatz SS e del CDS. Impianto di una clip in sede centrale (XTR) ed una clip mediale (NTR) alla prima con risultato ottimale. L'IM è ridotta a grado lieve, non aumento dopo manovra di Trendelemburg. Si rimuove il sistema di rilascio. Emostasi locale.</t>
+        </is>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>percutaneo</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1509,4 +2663,160 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>n_cartella</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>cognome</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>data_di_nascita</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>data_intervento</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ingresso_in_sala</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inizio_tempo_chirurgico</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tempi_cch_inizio_cec</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tempi_cch_clamp_ao</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempi_cch_declamp_ao</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tempi_cch_fine_cec</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>fine_tempo_chirurgico</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>uscita_di_sala</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>cec</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>cardioplegia</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_plegia</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>anestesia</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>farmaci_intraop</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>eventi_intraop</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>parametri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>12019013470</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COLOMBA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DE SIO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1004-01-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2903-01-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>